--- a/src/attributions/attributions_ig_traj_330.xlsx
+++ b/src/attributions/attributions_ig_traj_330.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG8"/>
+  <dimension ref="A1:GG17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,25 +999,25 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.6194875602266686</v>
+        <v>0.2208504462592836</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06367798764224827</v>
+        <v>-0.05890878519122555</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1221528769083262</v>
+        <v>-0.05303054350413461</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -1029,25 +1029,25 @@
         <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05384716492673947</v>
+        <v>-0.02543269672971675</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.202793458756444</v>
+        <v>0.1865665286380515</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.06549330437446281</v>
+        <v>0.0368035544352248</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>-0</v>
@@ -1056,16 +1056,16 @@
         <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1021020724536463</v>
+        <v>0.03610675782960398</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.008383886875442408</v>
+        <v>0.03601559597471601</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.05306648169693744</v>
+        <v>-0.0003158647106407779</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -1077,52 +1077,52 @@
         <v>-0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.001507543686501927</v>
+        <v>0.0981103427423053</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.01040322573825583</v>
+        <v>-0.1005426779089932</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.09184670129547647</v>
+        <v>0.1925415697293174</v>
       </c>
       <c r="AG2" t="n">
         <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.1690485301917014</v>
+        <v>0.1118537937291624</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.1403065897673105</v>
+        <v>-0.04120172598188631</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.1170094814116633</v>
+        <v>0.1928854673893693</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -1137,22 +1137,22 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.9568851336254893</v>
+        <v>0.3424042678561391</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.06218988250303957</v>
+        <v>-0.3014166099096467</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.2429803530570094</v>
+        <v>-0.0997989711642143</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
         <v>-0</v>
@@ -1161,157 +1161,157 @@
         <v>-0</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.06212827845485812</v>
+        <v>-0.006317308549902218</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.009107948736244998</v>
+        <v>-0.006684889512229914</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.1179888567075231</v>
+        <v>-0.005422929113788656</v>
       </c>
       <c r="BH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.2151096335578995</v>
+        <v>-0.04939441564497614</v>
       </c>
       <c r="BN2" t="n">
         <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.1256330171378054</v>
+        <v>-0.007443553298669588</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.224062833191389</v>
+        <v>0.1082736909312697</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.636262763941165</v>
+        <v>0.1640002032518</v>
       </c>
       <c r="BW2" t="n">
         <v>-0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.009851542518439418</v>
+        <v>-0.1068318295357829</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.159157971330107</v>
+        <v>-0.01862245531894648</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB2" t="n">
         <v>-0</v>
       </c>
       <c r="CC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.2762914475388283</v>
+        <v>-0.1775304879086704</v>
       </c>
       <c r="CF2" t="n">
         <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.07798607986709202</v>
+        <v>0.1179539196889748</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.08260151635584402</v>
+        <v>0.03253131408579215</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL2" t="n">
         <v>-0</v>
       </c>
       <c r="CM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.1016891777214308</v>
+        <v>-0.1451902504929437</v>
       </c>
       <c r="CO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.2128052839268964</v>
+        <v>0.08023347138906396</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.6211914471235902</v>
+        <v>-0.02673697348635155</v>
       </c>
       <c r="CR2" t="n">
         <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT2" t="n">
         <v>0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.3068738119359521</v>
+        <v>-0.2044829028651693</v>
       </c>
       <c r="CX2" t="n">
         <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0.1204920158481755</v>
+        <v>0.1287920685791925</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.03388895735703194</v>
+        <v>0.05529364859435505</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
         <v>-0</v>
@@ -1326,70 +1326,70 @@
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.301244219910308</v>
+        <v>-0.1949064680939093</v>
       </c>
       <c r="DG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0.2064532668576247</v>
+        <v>0.06510071188963905</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.07324027512370716</v>
+        <v>-0.02698850499102642</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.2957967158666627</v>
+        <v>-0.1452520582186959</v>
       </c>
       <c r="DP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.08023396208486278</v>
+        <v>0.1210143335291083</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.1793423404590819</v>
+        <v>-0.09026136221469844</v>
       </c>
       <c r="DS2" t="n">
         <v>-0</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.225479712073922</v>
+        <v>-0.07624755957423891</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.2396720064675233</v>
+        <v>0.00885399246085611</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.01897076231407441</v>
+        <v>-0.00408686361963499</v>
       </c>
       <c r="EB2" t="n">
         <v>-0</v>
@@ -1404,25 +1404,25 @@
         <v>-0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.305100358805739</v>
+        <v>-0.1666949164355829</v>
       </c>
       <c r="EH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>-0.05037630037555069</v>
+        <v>0.1017750246788853</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.183486494776537</v>
+        <v>0.06425085611042922</v>
       </c>
       <c r="EK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM2" t="n">
         <v>0</v>
@@ -1434,16 +1434,16 @@
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.0792592743902463</v>
+        <v>0.03369167033465142</v>
       </c>
       <c r="EQ2" t="n">
         <v>-0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.08880437189102285</v>
+        <v>0.05044521492994363</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.06377159212350068</v>
+        <v>-0.05828763058155921</v>
       </c>
       <c r="ET2" t="n">
         <v>0</v>
@@ -1452,28 +1452,28 @@
         <v>0</v>
       </c>
       <c r="EV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.3012267341609436</v>
+        <v>-0.2230718063455969</v>
       </c>
       <c r="EZ2" t="n">
         <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0.1094733120223672</v>
+        <v>0.1294726425238387</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.07879630257610311</v>
+        <v>0.02996637480077155</v>
       </c>
       <c r="FC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD2" t="n">
         <v>0</v>
@@ -1488,16 +1488,16 @@
         <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.002876600353635387</v>
+        <v>-0.08325820491896525</v>
       </c>
       <c r="FI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.0112108749361794</v>
+        <v>-0.04264178984974176</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.05873193352943057</v>
+        <v>-0.00375450669034533</v>
       </c>
       <c r="FL2" t="n">
         <v>0</v>
@@ -1512,66 +1512,66 @@
         <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.1882810715552427</v>
+        <v>-0.1689100894734265</v>
       </c>
       <c r="FR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>-0.3365635327690355</v>
+        <v>0.2867309804744327</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.244899875857684</v>
+        <v>0.09174918257778011</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY2" t="n">
         <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.101204526047084</v>
+        <v>-0.1809693683435382</v>
       </c>
       <c r="GA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB2" t="n">
-        <v>-0.002941328081368019</v>
+        <v>0.02507249521285625</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>-0.1678059912076217</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.3868461174128458</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -1580,88 +1580,88 @@
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>-0.09794248875839329</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0.2502396704229419</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.01572366984201707</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0.02522430369800323</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.02030351917961661</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.05936293937442537</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0.02334624228424238</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.07737631372073885</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0</v>
+        <v>-0.166185838805364</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0.1133511822452941</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-0.0008495128452366855</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>0.1968258690748055</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0</v>
+        <v>0.08614659329725233</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1670,79 +1670,79 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>0.312919546781718</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>-0.0809103379131825</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>0.1741793388268171</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0</v>
+        <v>0.03991436015037216</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>-0.08544269538073923</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>-0.04553521859854552</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>0.7086068310909885</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0</v>
+        <v>-0.03658598288797536</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0.3032804200066167</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0.01637070528661674</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>0.00751766178467719</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>0.02057398177974845</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
@@ -1751,25 +1751,25 @@
         <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>-0.08618291980820231</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>0.1675873397126078</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>0.1460653150504995</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO3" t="n">
         <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0</v>
+        <v>0.3844514382062931</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
@@ -1778,55 +1778,55 @@
         <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>0.251434393221576</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>-0.08765551387481292</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>0.4210507543403494</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0</v>
+        <v>-0.2758614537696416</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB3" t="n">
         <v>0</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>-0.4613793398429058</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>0.1256756732512286</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>-0.2779733317424815</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG3" t="n">
         <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0</v>
+        <v>0.02344815707181475</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
         <v>0</v>
@@ -1835,13 +1835,13 @@
         <v>0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>0.207516084134147</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>-0.09181661930151147</v>
       </c>
       <c r="CN3" t="n">
-        <v>0</v>
+        <v>-0.6051212705179606</v>
       </c>
       <c r="CO3" t="n">
         <v>0</v>
@@ -1850,25 +1850,25 @@
         <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0</v>
+        <v>-0.3897219428686788</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT3" t="n">
         <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>0.2080702814428424</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>0.09286710789131131</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>-0.289348642683102</v>
       </c>
       <c r="CX3" t="n">
         <v>0</v>
@@ -1877,133 +1877,133 @@
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>-0.03411547643327354</v>
       </c>
       <c r="DA3" t="n">
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>0.2367839992776707</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>0.02246231587124348</v>
       </c>
       <c r="DF3" t="n">
-        <v>0</v>
+        <v>-0.5323401891203696</v>
       </c>
       <c r="DG3" t="n">
         <v>0</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0</v>
+        <v>-0.399854217547387</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>0.1397184801727825</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>-0.006926524994154333</v>
       </c>
       <c r="DO3" t="n">
-        <v>0</v>
+        <v>-0.2321722373406863</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
         <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0</v>
+        <v>0.02811211086611122</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>0.05660440757338725</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>-0.02399771872502116</v>
       </c>
       <c r="DX3" t="n">
-        <v>0</v>
+        <v>-0.3149505419883891</v>
       </c>
       <c r="DY3" t="n">
         <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0</v>
+        <v>-0.2703791013545375</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED3" t="n">
         <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>-0.09162190522336727</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>0.2219702451541671</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>-0.125543604692072</v>
       </c>
       <c r="EH3" t="n">
         <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0</v>
+        <v>-0.03314817006085602</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
         <v>0</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>0.1833759602746668</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>0.1048546573834591</v>
       </c>
       <c r="EP3" t="n">
-        <v>0</v>
+        <v>-0.1046640774710213</v>
       </c>
       <c r="EQ3" t="n">
         <v>0</v>
@@ -2012,10 +2012,10 @@
         <v>-0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0</v>
+        <v>-0.08729921991555281</v>
       </c>
       <c r="ET3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU3" t="n">
         <v>0</v>
@@ -2024,25 +2024,25 @@
         <v>0</v>
       </c>
       <c r="EW3" t="n">
-        <v>0</v>
+        <v>0.02296758905228174</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>0.141721356603897</v>
       </c>
       <c r="EY3" t="n">
-        <v>0</v>
+        <v>-0.3574804079024991</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA3" t="n">
         <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0</v>
+        <v>-0.01116188175323243</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD3" t="n">
         <v>0</v>
@@ -2051,22 +2051,22 @@
         <v>0</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>0.2586552531313215</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>0.02414533376088778</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>-0.2655701425998804</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ3" t="n">
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0</v>
+        <v>0.03334189719930685</v>
       </c>
       <c r="FL3" t="n">
         <v>0</v>
@@ -2078,13 +2078,13 @@
         <v>0</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>0.2723429871283096</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>0.1746559419129515</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>-0.2479849681473317</v>
       </c>
       <c r="FR3" t="n">
         <v>0</v>
@@ -2093,28 +2093,28 @@
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0</v>
+        <v>0.49795423510524</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV3" t="n">
         <v>0</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>0.02642982169753386</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>0.2336397707600214</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0</v>
+        <v>-0.2473428962058922</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB3" t="n">
         <v>0</v>
@@ -2126,13 +2126,13 @@
         <v>0</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>0.4143100303278182</v>
       </c>
     </row>
     <row r="4">
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.2209918340009237</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2149,16 +2149,16 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0.04310332702059462</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>-0.175978581156215</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.0004617429227651532</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2176,43 +2176,43 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.138135790775077e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0.001199411132690204</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.04940842763203496</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0</v>
+        <v>-0.02512289420585817</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0.007834172396092907</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>-0.001921336179779491</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -2230,25 +2230,25 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0</v>
+        <v>-0.04383480103093423</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0</v>
+        <v>0.02995350831060203</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>0.1025238488404243</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2257,16 +2257,16 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0</v>
+        <v>0.06541887834509137</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0</v>
+        <v>-0.04859803687175521</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>0.4198265575807516</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2284,25 +2284,25 @@
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0</v>
+        <v>0.006471567129326535</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0</v>
+        <v>-0.1162869647309495</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>-0.00157332371028057</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -2311,16 +2311,16 @@
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>-0.001563955970303722</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>-0.05641816016420897</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
@@ -2329,25 +2329,25 @@
         <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>0.001734538946702084</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0</v>
+        <v>0.1029710946844375</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0</v>
+        <v>0.05336671697590345</v>
       </c>
       <c r="BR4" t="n">
         <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
         <v>0</v>
@@ -2356,22 +2356,22 @@
         <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>0.2027923842982235</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0</v>
+        <v>0.00810860618707126</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>-0.1253508794166782</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
         <v>0</v>
@@ -2380,22 +2380,22 @@
         <v>0</v>
       </c>
       <c r="CD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>0</v>
+        <v>-0.1367110240287453</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0</v>
+        <v>-0.02927485332760158</v>
       </c>
       <c r="CI4" t="n">
-        <v>-0</v>
+        <v>0.1049193679477737</v>
       </c>
       <c r="CJ4" t="n">
         <v>0</v>
@@ -2410,52 +2410,52 @@
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0</v>
+        <v>-0.09817832170734855</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0</v>
+        <v>-0.02608379897333252</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0</v>
+        <v>0.1318622633579996</v>
       </c>
       <c r="CS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>0</v>
+        <v>-0.1350420577427947</v>
       </c>
       <c r="CX4" t="n">
         <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0</v>
+        <v>-0.02558432221437081</v>
       </c>
       <c r="DA4" t="n">
-        <v>0</v>
+        <v>0.119288071528799</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD4" t="n">
         <v>0</v>
@@ -2464,7 +2464,7 @@
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>0</v>
+        <v>-0.07520445711318129</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
@@ -2473,10 +2473,10 @@
         <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0</v>
+        <v>-0.09428210796676453</v>
       </c>
       <c r="DJ4" t="n">
-        <v>-0</v>
+        <v>0.06203006180506664</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
@@ -2485,31 +2485,31 @@
         <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>0</v>
+        <v>-0.05580371735647581</v>
       </c>
       <c r="DP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ4" t="n">
         <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0</v>
+        <v>-0.07097529207301467</v>
       </c>
       <c r="DS4" t="n">
-        <v>-0</v>
+        <v>-0.1108985441480198</v>
       </c>
       <c r="DT4" t="n">
         <v>0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
@@ -2518,34 +2518,34 @@
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0</v>
+        <v>-0.08206240675488169</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>0</v>
+        <v>-0.04869131147535913</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>0.0851086327035821</v>
       </c>
       <c r="EC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED4" t="n">
         <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG4" t="n">
-        <v>0</v>
+        <v>-0.08301007596233975</v>
       </c>
       <c r="EH4" t="n">
         <v>0</v>
@@ -2554,64 +2554,64 @@
         <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0</v>
+        <v>-0.04413849705925936</v>
       </c>
       <c r="EK4" t="n">
-        <v>-0</v>
+        <v>0.06010766491452148</v>
       </c>
       <c r="EL4" t="n">
         <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN4" t="n">
         <v>0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0</v>
+        <v>0.01612637507833577</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
         <v>0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0</v>
+        <v>0.0430040214076368</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0</v>
+        <v>0.04544906690968395</v>
       </c>
       <c r="EU4" t="n">
         <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
         <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>0</v>
+        <v>-0.153119212612188</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0</v>
+        <v>-0.06551780041445923</v>
       </c>
       <c r="FC4" t="n">
-        <v>-0</v>
+        <v>0.09514198878775028</v>
       </c>
       <c r="FD4" t="n">
         <v>0</v>
@@ -2620,13 +2620,13 @@
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0</v>
+        <v>-0.1108420661464574</v>
       </c>
       <c r="FI4" t="n">
         <v>0</v>
@@ -2635,10 +2635,10 @@
         <v>0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0</v>
+        <v>0.03861398494525476</v>
       </c>
       <c r="FL4" t="n">
-        <v>-0</v>
+        <v>0.05461152517068273</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2650,55 +2650,55 @@
         <v>0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0</v>
+        <v>-0.2193203942584719</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0</v>
+        <v>-0.1169211336042286</v>
       </c>
       <c r="FU4" t="n">
-        <v>-0</v>
+        <v>-0.06368162615381273</v>
       </c>
       <c r="FV4" t="n">
         <v>0</v>
       </c>
       <c r="FW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
         <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0</v>
+        <v>-0.07418526887395048</v>
       </c>
       <c r="GA4" t="n">
         <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>0</v>
+        <v>0.04761949956880428</v>
       </c>
       <c r="GE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
         <v>0</v>
@@ -2709,22 +2709,22 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.2803734328403151</v>
       </c>
       <c r="C5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-0.09032211404399322</v>
       </c>
       <c r="E5" t="n">
-        <v>-0</v>
+        <v>-0.02333702061308306</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -2736,22 +2736,22 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.02862337581039472</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.02607940613084044</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-7.425457317025105e-05</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -2760,19 +2760,19 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.06524400539287033</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.0225482934662149</v>
       </c>
       <c r="W5" t="n">
-        <v>-0</v>
+        <v>-0.006550036925485321</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -2787,22 +2787,22 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>0.09256435725756133</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>-0.1523420746783723</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0</v>
+        <v>0.1543367062632761</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -2814,19 +2814,19 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>0.130087572046215</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>-0.04408985880702426</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0</v>
+        <v>0.1438667788287805</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
@@ -2838,55 +2838,55 @@
         <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>0.4292108527625018</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>-0.2137159269199885</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0</v>
+        <v>-0.09736618853897414</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>-0.0251415296867609</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>0.001800014954484901</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>-0.004367171862906838</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ5" t="n">
         <v>0</v>
@@ -2895,46 +2895,46 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>-0.04586736549045915</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>0.04522053056790648</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0</v>
+        <v>0.11340045066378</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR5" t="n">
         <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>0.237474855475802</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>-0.06949922712084911</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0</v>
+        <v>-0.007638262947210048</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -2952,79 +2952,79 @@
         <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>0</v>
+        <v>-0.1861153166824545</v>
       </c>
       <c r="CF5" t="n">
         <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0</v>
+        <v>0.1383637887820109</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0</v>
+        <v>-0.004294975882091938</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
         <v>0</v>
       </c>
       <c r="CK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0</v>
+        <v>-0.1390126736194373</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>0.1232597493904777</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0</v>
+        <v>-0.03945615146654843</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>0</v>
+        <v>-0.1903447963292414</v>
       </c>
       <c r="CX5" t="n">
         <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0</v>
+        <v>0.1363450260081356</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0</v>
+        <v>0.003050284339962956</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD5" t="n">
         <v>0</v>
@@ -3033,19 +3033,19 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0</v>
+        <v>-0.06006404471059982</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0</v>
+        <v>0.05025625782904038</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0</v>
+        <v>-0.06461103578557217</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
@@ -3054,31 +3054,31 @@
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>0</v>
+        <v>-0.1278871788642497</v>
       </c>
       <c r="DP5" t="n">
         <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0</v>
+        <v>0.1268468615906949</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0</v>
+        <v>-0.1069713204777194</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
@@ -3087,19 +3087,19 @@
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0</v>
+        <v>-0.06545913369110208</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0.1054145620086022</v>
       </c>
       <c r="EA5" t="n">
-        <v>0</v>
+        <v>-0.01515292497519366</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
         <v>0</v>
@@ -3108,49 +3108,49 @@
         <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>0</v>
+        <v>-0.1528205627944949</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0</v>
+        <v>0.1331539550091421</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0</v>
+        <v>0.01454131497273786</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM5" t="n">
         <v>0</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0</v>
+        <v>0.05881203587770463</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0</v>
+        <v>0.03484769888724153</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0</v>
+        <v>-0.05445674128019017</v>
       </c>
       <c r="ET5" t="n">
         <v>0</v>
@@ -3159,28 +3159,28 @@
         <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX5" t="n">
         <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>0</v>
+        <v>-0.2103504118546949</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0</v>
+        <v>0.148279828714101</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0</v>
+        <v>-0.01409886389444536</v>
       </c>
       <c r="FC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD5" t="n">
         <v>0</v>
@@ -3189,58 +3189,58 @@
         <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0</v>
+        <v>-0.0925241962936582</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0</v>
+        <v>-0.01643593232320229</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0</v>
+        <v>-0.00937956816128048</v>
       </c>
       <c r="FL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0</v>
+        <v>-0.308871744271253</v>
       </c>
       <c r="FR5" t="n">
         <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0</v>
+        <v>0.2509526048972043</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0</v>
+        <v>0.1113141778615576</v>
       </c>
       <c r="FU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV5" t="n">
         <v>0</v>
       </c>
       <c r="FW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX5" t="n">
         <v>0</v>
@@ -3249,25 +3249,25 @@
         <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0</v>
+        <v>-0.1729418316998493</v>
       </c>
       <c r="GA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB5" t="n">
-        <v>0</v>
+        <v>0.07954912923822298</v>
       </c>
       <c r="GC5" t="n">
         <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
         <v>0</v>
@@ -3275,109 +3275,109 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.00570417209495767</v>
+        <v>-0.1497052794152744</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0</v>
+        <v>0.01618157223031573</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.005873891991258247</v>
+        <v>0.005692144361801954</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1159842490842065</v>
+        <v>0.2633241622383614</v>
       </c>
       <c r="G6" t="n">
         <v>-0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0105619604229925</v>
+        <v>-0.03502408023153366</v>
       </c>
       <c r="L6" t="n">
         <v>-0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0</v>
+        <v>-0.009079197144075825</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.01101604013698649</v>
+        <v>0.007799148070624075</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02183370899887525</v>
+        <v>0.03288369951880358</v>
       </c>
       <c r="P6" t="n">
         <v>-0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.02808469187000387</v>
+        <v>0.005601587593605658</v>
       </c>
       <c r="U6" t="n">
         <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.01191160662941394</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.02491132783836152</v>
+        <v>-0.02432226489543977</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.02445799578379134</v>
+        <v>0.09954393580980489</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.02053272840372852</v>
+        <v>-0.03809742446310128</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0.1584012295405557</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.04859370102554861</v>
+        <v>-0.08738433030665878</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.006713342436312168</v>
+        <v>-0.1293574220236601</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
@@ -3386,49 +3386,49 @@
         <v>-0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.01419508942509601</v>
+        <v>-0.1086632092337428</v>
       </c>
       <c r="AM6" t="n">
         <v>-0</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>-0.007028664594831011</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.007745044917949841</v>
+        <v>-0.1525229447634713</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.06994092781293372</v>
+        <v>0.1050838634661078</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT6" t="n">
         <v>-0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.03246164469356116</v>
+        <v>-0.3965419396956423</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>0.06454104141209484</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.1102943074647617</v>
+        <v>-0.02522436695539163</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.2061435510894096</v>
+        <v>0.3405853246381703</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -3440,19 +3440,19 @@
         <v>-0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.009724074708808702</v>
+        <v>0.04983772463882982</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0</v>
+        <v>0.0336750023145921</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.582639470001912e-12</v>
+        <v>0.01820482359690909</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.006275176720587779</v>
+        <v>0.01828669984843034</v>
       </c>
       <c r="BI6" t="n">
         <v>-0</v>
@@ -3461,28 +3461,28 @@
         <v>-0</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL6" t="n">
         <v>-0</v>
       </c>
       <c r="BM6" t="n">
-        <v>-1.053787501473e-10</v>
+        <v>-0.0003126832643246112</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>0.0350526281009199</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.04378266635261355</v>
+        <v>-0.08304722702231009</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.02783048150174789</v>
+        <v>-0.03938179910417751</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>0</v>
@@ -3491,49 +3491,49 @@
         <v>-0</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.02953544019497525</v>
+        <v>-0.06769918651109168</v>
       </c>
       <c r="BW6" t="n">
         <v>-0</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>-0.02750516800041851</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.03278674820710596</v>
+        <v>-0.01338456602300929</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.07281607091917369</v>
+        <v>0.2891966544488153</v>
       </c>
       <c r="CA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC6" t="n">
         <v>-0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.02136584330833587</v>
+        <v>0.17978440320387</v>
       </c>
       <c r="CF6" t="n">
         <v>0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0</v>
+        <v>-0.02793451542093427</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.005048616678727707</v>
+        <v>0.00955038382902379</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.07149970346151548</v>
+        <v>-0.1250958557272552</v>
       </c>
       <c r="CJ6" t="n">
         <v>0</v>
@@ -3542,28 +3542,28 @@
         <v>0</v>
       </c>
       <c r="CL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.02189307666800963</v>
+        <v>0.1343776684648922</v>
       </c>
       <c r="CO6" t="n">
         <v>0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0</v>
+        <v>-0.1253780955835693</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.06296780692935852</v>
+        <v>-0.04685051867346665</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.001226979034279499</v>
+        <v>-0.1411650140894448</v>
       </c>
       <c r="CS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT6" t="n">
         <v>-0</v>
@@ -3572,22 +3572,22 @@
         <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.003653577419964127</v>
+        <v>0.1951303316905101</v>
       </c>
       <c r="CX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0</v>
+        <v>-0.02585400901334147</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.006187217633195493</v>
+        <v>-0.04225594141312711</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.07348966002299916</v>
+        <v>-0.1332784179428679</v>
       </c>
       <c r="DB6" t="n">
         <v>-0</v>
@@ -3596,52 +3596,52 @@
         <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.06907885222475259</v>
+        <v>0.05245294781528531</v>
       </c>
       <c r="DG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>0</v>
+        <v>-0.02835816273100395</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.03396861518787253</v>
+        <v>0.009027528542153176</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.00291315713255</v>
+        <v>-0.09776203200291526</v>
       </c>
       <c r="DK6" t="n">
         <v>-0</v>
       </c>
       <c r="DL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM6" t="n">
         <v>0</v>
       </c>
       <c r="DN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.03824213323322637</v>
+        <v>0.1150654334955916</v>
       </c>
       <c r="DP6" t="n">
         <v>0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>-0.0756787577492172</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.004688377783461982</v>
+        <v>0.04583068108759976</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.0015242372367263</v>
+        <v>-0.066444495537375</v>
       </c>
       <c r="DT6" t="n">
         <v>0</v>
@@ -3650,163 +3650,163 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.02021225408092616</v>
+        <v>0.1231905484024092</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0</v>
+        <v>0.09866747063654371</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.05346792663112952</v>
+        <v>0.01945772817760819</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.0002195866081763013</v>
+        <v>0.1433724703787378</v>
       </c>
       <c r="EC6" t="n">
         <v>0</v>
       </c>
       <c r="ED6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.01778891570126348</v>
+        <v>0.1632594642322853</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0.06129803926695425</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.0121164715058656</v>
+        <v>-0.07314998833177171</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.09907364815762525</v>
+        <v>-0.06602472976507759</v>
       </c>
       <c r="EL6" t="n">
         <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.04184936565223609</v>
+        <v>-0.04115572488711791</v>
       </c>
       <c r="EQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0</v>
+        <v>0.03280288319761911</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.05383367781518656</v>
+        <v>0.02898369931713944</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.0041564894645212</v>
+        <v>-0.03362323743762458</v>
       </c>
       <c r="EU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.01382603453370663</v>
+        <v>0.2034630880240515</v>
       </c>
       <c r="EZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0</v>
+        <v>-0.02750929221887065</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.01019114679844707</v>
+        <v>0.004866716463771499</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.07191428862273774</v>
+        <v>-0.1480007148025803</v>
       </c>
       <c r="FD6" t="n">
         <v>0</v>
       </c>
       <c r="FE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.00325402296433325</v>
+        <v>0.06325489796410343</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0</v>
+        <v>0.04827379785721468</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.02919815912573894</v>
+        <v>0.05601981621283696</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.08974315175879359</v>
+        <v>-0.06496823216003259</v>
       </c>
       <c r="FM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN6" t="n">
         <v>0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.0203831460949928</v>
+        <v>0.1133323559318354</v>
       </c>
       <c r="FR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS6" t="n">
-        <v>-0</v>
+        <v>-0.1741957903184827</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.08688777065583868</v>
+        <v>-0.04986032405795669</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.02364452492292085</v>
+        <v>-0.05373115239288104</v>
       </c>
       <c r="FV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW6" t="n">
         <v>-0</v>
@@ -3818,25 +3818,25 @@
         <v>-0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.001258777966208644</v>
+        <v>0.1513244238788105</v>
       </c>
       <c r="GA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB6" t="n">
-        <v>-0</v>
+        <v>0.04529410887598041</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.02690178174332217</v>
+        <v>-0.09443028991262425</v>
       </c>
       <c r="GE6" t="n">
         <v>0</v>
       </c>
       <c r="GF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG6" t="n">
         <v>0</v>
@@ -3844,22 +3844,22 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.01945414312676462</v>
+        <v>0.5281656959034464</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1406410982512745</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001806605722112905</v>
+        <v>0.1116806156316556</v>
       </c>
       <c r="F7" t="n">
-        <v>-0</v>
+        <v>-0.2937768770477889</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -3868,79 +3868,79 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0127351836783106</v>
+        <v>0.1772786485187926</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1449165285239918</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.00818278336320357</v>
+        <v>-0.007018764388266334</v>
       </c>
       <c r="O7" t="n">
-        <v>-0</v>
+        <v>0.004487923887024258</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0268147651207136</v>
+        <v>0.04962348575671057</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.002751873197356207</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.01364077860646014</v>
+        <v>-0.04399238244287605</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.05043412262440494</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.02621299588904676</v>
+        <v>0.08439502731330406</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.005640563858975395</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.005202552399551828</v>
+        <v>-0.1476237916455069</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0</v>
+        <v>0.07559337621404248</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -3949,112 +3949,112 @@
         <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.02601882017803615</v>
+        <v>0.1893704434583371</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.02400860901942677</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.05068899992800726</v>
+        <v>0.1115370960034087</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0</v>
+        <v>-0.1924536877938864</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.1082463403844037</v>
+        <v>0.8445466808758187</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.05865462127426319</v>
+        <v>-0</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.02098103754917886</v>
+        <v>-0.322861244269892</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0</v>
+        <v>-0.3241446830630472</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.001194558234772801</v>
+        <v>0.01615681131740879</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.04876704839039633</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.008317463691807509</v>
+        <v>0.04166864040648102</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>-0.06472445645178539</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
         <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
         <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.642289361844906e-11</v>
+        <v>0.06545758505450708</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.007387420351920032</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>-1.955671509557032e-10</v>
+        <v>0.1485442492003262</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>0.1685471827699757</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT7" t="n">
         <v>0</v>
@@ -4063,25 +4063,25 @@
         <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.02713192459480911</v>
+        <v>0.5408591883236662</v>
       </c>
       <c r="BW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.003824703048566659</v>
+        <v>-0</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.01470035537173102</v>
+        <v>0.03019211670235639</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>-0.2862573563027829</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC7" t="n">
         <v>0</v>
@@ -4090,49 +4090,49 @@
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.00534050831930029</v>
+        <v>-0.3193430100153254</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.02672383868493871</v>
+        <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.01493036755358043</v>
+        <v>-0.03961272192003638</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0</v>
+        <v>0.2281116716697324</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>-0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.005466080607838362</v>
+        <v>-0.4525529539368244</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.01984222359291601</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.03608564034504286</v>
+        <v>0.04462471763347353</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0</v>
+        <v>0.2169905039803631</v>
       </c>
       <c r="CS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT7" t="n">
         <v>0</v>
@@ -4141,55 +4141,55 @@
         <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.01459528299041554</v>
+        <v>-0.3123439158238912</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>-0.02433128818490321</v>
+        <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.009108602364349532</v>
+        <v>-0.07721945050758128</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0.2128747849744066</v>
       </c>
       <c r="DB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.03822983201010024</v>
+        <v>-0.04954227311003563</v>
       </c>
       <c r="DG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.003378023245644104</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.04619209070124566</v>
+        <v>-0.05415953356908269</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0</v>
+        <v>0.1342953709611549</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM7" t="n">
         <v>-0</v>
@@ -4198,22 +4198,22 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.02468804116360183</v>
+        <v>-0.1731203014981875</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.0507415444210032</v>
+        <v>-0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.02541580099976479</v>
+        <v>0.01029427838448558</v>
       </c>
       <c r="DS7" t="n">
-        <v>-0</v>
+        <v>0.1176958509710202</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
         <v>-0</v>
@@ -4222,22 +4222,22 @@
         <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.03928716658593787</v>
+        <v>0.240452598860751</v>
       </c>
       <c r="DY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.01241156254673428</v>
+        <v>0</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.03392614421858754</v>
+        <v>-0.1059290744563497</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0.1683168584202561</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
@@ -4252,52 +4252,52 @@
         <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.02855248501494874</v>
+        <v>-0.05435145699274935</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.05799468598945105</v>
+        <v>0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.005435550178124336</v>
+        <v>-0.1717644135707545</v>
       </c>
       <c r="EK7" t="n">
-        <v>-0</v>
+        <v>0.1095892319064162</v>
       </c>
       <c r="EL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN7" t="n">
         <v>0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.01329402694149501</v>
+        <v>-0.1424164354634693</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0.01537142975346168</v>
+        <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.007837460415341911</v>
+        <v>-0.1730344884169388</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>-0.02366571795643371</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW7" t="n">
         <v>0</v>
@@ -4306,52 +4306,52 @@
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.01537654038636431</v>
+        <v>-0.3209077727888594</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>-0.01699213218998945</v>
+        <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.009012459532403511</v>
+        <v>-0.1164926734728695</v>
       </c>
       <c r="FC7" t="n">
-        <v>0</v>
+        <v>0.1839125525596312</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
         <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.003232980152717903</v>
+        <v>-0.1790238160610123</v>
       </c>
       <c r="FI7" t="n">
         <v>0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>-0.01661923304378248</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.003821997163269259</v>
+        <v>-0.05051113788874966</v>
       </c>
       <c r="FL7" t="n">
-        <v>0</v>
+        <v>0.2289505439731969</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
         <v>-0</v>
@@ -4360,19 +4360,19 @@
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.02039701945482958</v>
+        <v>-0.1043520282128313</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>-0.04124610025736609</v>
+        <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.02019602656499478</v>
+        <v>-0.03399980822745015</v>
       </c>
       <c r="FU7" t="n">
-        <v>0</v>
+        <v>0.001833584127843375</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
@@ -4387,25 +4387,25 @@
         <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.02848555368315924</v>
+        <v>-0.1272922210527945</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.0349238162517933</v>
+        <v>-0</v>
       </c>
       <c r="GC7" t="n">
         <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>0</v>
+        <v>0.1241948321790447</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG7" t="n">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>-0.5457196650884054</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.4107180434865164</v>
       </c>
       <c r="E8" t="n">
-        <v>-0</v>
+        <v>-0.0320540020252096</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -4437,22 +4437,22 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.1637483430859588</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.2031707134306045</v>
       </c>
       <c r="N8" t="n">
-        <v>-0</v>
+        <v>-0.005932979708433234</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -4470,19 +4470,19 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.03293052810119378</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.02615898758835906</v>
       </c>
       <c r="W8" t="n">
-        <v>-0</v>
+        <v>-0.01743409835591378</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -4491,52 +4491,52 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>-0.03912465324989785</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>0.04678410913178788</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0</v>
+        <v>-0.1492299700225835</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>-0.3290524843135549</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>0.05486862629031894</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0</v>
+        <v>-0.376288010888136</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ8" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>-0.4496782287510067</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>0.2068467193503369</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0</v>
+        <v>-0.007547383367934136</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB8" t="n">
         <v>0</v>
@@ -4578,49 +4578,49 @@
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>-0.04208245924275023</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>0.01331621691850333</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0</v>
+        <v>0.0008642214717937082</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI8" t="n">
         <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL8" t="n">
         <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>0.1906629849034809</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>-0.09553374879115845</v>
       </c>
       <c r="BP8" t="n">
-        <v>-0</v>
+        <v>0.06495014785040765</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS8" t="n">
         <v>0</v>
@@ -4632,43 +4632,43 @@
         <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>-0.4467331578771233</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>0.2814483367634531</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0</v>
+        <v>-0.1719629424395923</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA8" t="n">
         <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0</v>
+        <v>0.3835988716279848</v>
       </c>
       <c r="CF8" t="n">
         <v>0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0</v>
+        <v>-0.24307542563902</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0</v>
+        <v>0.09066341956152218</v>
       </c>
       <c r="CI8" t="n">
         <v>0</v>
@@ -4683,19 +4683,19 @@
         <v>0</v>
       </c>
       <c r="CM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN8" t="n">
-        <v>0</v>
+        <v>0.3788118473447046</v>
       </c>
       <c r="CO8" t="n">
         <v>0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0.2980207719977165</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0</v>
+        <v>0.1741550825137216</v>
       </c>
       <c r="CR8" t="n">
         <v>0</v>
@@ -4710,46 +4710,46 @@
         <v>0</v>
       </c>
       <c r="CV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>0</v>
+        <v>0.3736402605679572</v>
       </c>
       <c r="CX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0</v>
+        <v>-0.2259056036232523</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0</v>
+        <v>0.05121085773532225</v>
       </c>
       <c r="DA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0</v>
+        <v>0.01498363429770252</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0</v>
+        <v>-0.04018937712639504</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0</v>
+        <v>0.04853016063977204</v>
       </c>
       <c r="DJ8" t="n">
         <v>0</v>
@@ -4758,28 +4758,28 @@
         <v>0</v>
       </c>
       <c r="DL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM8" t="n">
         <v>0</v>
       </c>
       <c r="DN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>0</v>
+        <v>0.2156614688857288</v>
       </c>
       <c r="DP8" t="n">
         <v>0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0</v>
+        <v>-0.1636737734299462</v>
       </c>
       <c r="DR8" t="n">
-        <v>-0</v>
+        <v>0.03331724431497225</v>
       </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT8" t="n">
         <v>0</v>
@@ -4788,22 +4788,22 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0</v>
+        <v>0.2508481849597337</v>
       </c>
       <c r="DY8" t="n">
         <v>0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0</v>
+        <v>0.1671299005831074</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0</v>
+        <v>0.02934198351719694</v>
       </c>
       <c r="EB8" t="n">
         <v>0</v>
@@ -4812,61 +4812,61 @@
         <v>0</v>
       </c>
       <c r="ED8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE8" t="n">
         <v>0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>0</v>
+        <v>0.2646518816863817</v>
       </c>
       <c r="EH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0</v>
+        <v>-0.2297971409717142</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0</v>
+        <v>0.0121635850814012</v>
       </c>
       <c r="EK8" t="n">
         <v>0</v>
       </c>
       <c r="EL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>0</v>
+        <v>0.339066269417799</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0</v>
+        <v>-0.1335937709885553</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0</v>
+        <v>-0.1365827545016361</v>
       </c>
       <c r="ET8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW8" t="n">
         <v>0</v>
@@ -4875,25 +4875,25 @@
         <v>0</v>
       </c>
       <c r="EY8" t="n">
-        <v>0</v>
+        <v>0.3998283915643955</v>
       </c>
       <c r="EZ8" t="n">
         <v>0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0</v>
+        <v>-0.2742674392389964</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0</v>
+        <v>0.07631366252050391</v>
       </c>
       <c r="FC8" t="n">
         <v>0</v>
       </c>
       <c r="FD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF8" t="n">
         <v>0</v>
@@ -4902,16 +4902,16 @@
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>0</v>
+        <v>0.05356272290542063</v>
       </c>
       <c r="FI8" t="n">
         <v>0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0</v>
+        <v>-0.03160206808626044</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0</v>
+        <v>0.3845110969466012</v>
       </c>
       <c r="FL8" t="n">
         <v>0</v>
@@ -4929,16 +4929,16 @@
         <v>0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0</v>
+        <v>-0.0112344370973818</v>
       </c>
       <c r="FR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0</v>
+        <v>0.04510155372756511</v>
       </c>
       <c r="FT8" t="n">
-        <v>-0</v>
+        <v>0.07042125305862844</v>
       </c>
       <c r="FU8" t="n">
         <v>0</v>
@@ -4950,25 +4950,25 @@
         <v>0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
         <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0</v>
+        <v>0.2594422896249713</v>
       </c>
       <c r="GA8" t="n">
         <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>0</v>
+        <v>-0.3610876226068698</v>
       </c>
       <c r="GC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE8" t="n">
         <v>0</v>
@@ -4977,6 +4977,5127 @@
         <v>0</v>
       </c>
       <c r="GG8" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.2183539451476497</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.08784651724961051</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.02669976072399244</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.09256368865195201</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.008366293393501024</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.02519800934203897</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.03597822020275677</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.0191633078859368</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.04848238453132938</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-0.02364616462448322</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.06672735274123018</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.08482669189565932</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.09672731601102678</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.01496636747527096</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.06902906317050309</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.2600998482446124</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-0.03596167475866113</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-0.1210813579162695</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-0.009255497649392135</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.0007326529704474172</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-0.01332743472288633</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>-0.01288935888933821</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.0002766741090503657</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.06481382805165756</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.1873305495140359</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>-0.09163820734764255</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>-0.02455882335296199</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>-0.09423190516313289</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.06362472377938948</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.01551393014464244</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>-0.07794031967236188</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.08953751782941237</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.03781624145055152</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>-0.09247519144274637</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.06730108521059515</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0.01442014679096143</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0.003112174815130873</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.0150511781156988</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>-0.03866478860418437</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>-0.05791891649557802</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>-0.01176024178873872</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>-0.007207854064189963</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.08393436212077429</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.03594064270488417</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>-0.07454503663860224</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>-0.0495870797112623</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.05856435820876767</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>0.01698095629039901</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>-0.03986683437926694</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>0.05452924840971168</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>-0.02660631516206833</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>-0.0974779713734345</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0.07255416195614338</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>-0.00166481132365308</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>-0.02143477387932599</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.04062153230752507</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>-0.03925011179581708</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>0.00914928195777647</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0.08788678793494081</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>-0.01157723687015044</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>-0.07796487328060303</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>0.03672524783598674</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.3647806793238299</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.172036741715225</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01968429395090859</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.2183298321620929</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.02217985210314379</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.002924705141801217</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.1016377250136189</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-0.02922826636402784</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.0691903113895815</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.06636456577642461</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-0.173719828905508</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.0373524129183398</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.1479810468036685</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-0.07966742889036647</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.1138387768089732</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.3695804843578664</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-0.152308901954658</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-0.1137689097679482</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-0.01617406426559779</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-0.02923407922887424</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-0.02218312207148299</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>-0.03116865778580338</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0.03884501496101608</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.02711383900795365</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0.327082976889236</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>-0.1146176438750104</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-0.01424526978808908</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>-0.1396795763294643</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0.1470726399942006</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>-0.04254836521647105</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>-0.1298057512778343</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0.2248686083792075</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0.02927684884562921</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>-0.1285504083555058</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0.1408212952413083</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>-0.02884671728370796</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>-0.03811654224551935</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0.01736056773571083</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0.005380772385159763</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>-0.07924915251009387</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0.06638603440898624</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>-0.01112876349694857</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>-0.005933609110331424</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>-0.09247220723306046</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0.1089573596793195</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>-0.08750035412337751</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0.1098907892894518</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>0.0115433616085429</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>-0.08446253302355194</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>0.06189068000717168</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>-0.03677841590866018</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>-0.1546360374439853</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>0.161990290820082</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>-0.05172216921175717</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>-0.1230854776103581</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>0.09742313101848125</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>-0.004779892956332153</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>-0.01614694594528322</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>-0.168954940891126</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>-0.02410282736933757</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>-0.1131176495357851</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>0.08896809644111335</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.627422820536647</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.06061191564797961</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.3559869063142942</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.4848470099800309</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.07477875402112276</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.1248566387190366</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.1865836190134013</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.1508150897546938</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.054449992586172</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.02451221587952385</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.3043818300567229</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-0.08725303996372012</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.2047296173217211</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.05375847318474691</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.18902297130363</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.8549474041771488</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-0.2276815909294671</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.3443997222646378</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-0.06715582659037572</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>-0.06485595659530104</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-0.06604753806436144</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.0822693464709838</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0.1436962341524636</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0.07772264146023329</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.5563287333754479</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>-0.07118081701521775</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>-0.2323851639056316</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>-0.2479423257840932</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>-0.02800688302190992</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.1608544468760856</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>-0.3206695496005732</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0.1436771340074288</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>0.1762073625745528</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>-0.2196143630494782</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>-0.0466529040804157</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0.1646349066419909</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>-0.04056075903832509</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>-0.2390961412322847</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0.005237428461781487</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>-0.06403660509094541</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>-0.05251297355714121</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0.02654311202393523</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>0.1552989774217814</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>-0.04428079943792719</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>0.05495848003892043</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>-0.0548734780467573</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>-0.1350478032104411</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>0.06551998943514274</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>-0.1124493129546077</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>-0.1804588040648966</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>0.1325432674203112</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>-0.2611165978457194</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>-0.07421597977614532</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>0.1393396736848286</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>-0.2070471483929382</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>0.08820371317209454</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>0.2355773998782035</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>-0.02774485721425285</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>0.0007724081856934323</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>0.1548384933794067</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>-0.1212523038078352</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>0.04147103644037487</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.2077414505562488</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.01466234705374211</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.1077644325869491</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.1794941332711215</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.02753071641080561</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.04495021081227519</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.06180007958870848</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.0558993875343902</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.02169353517665368</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.03144323551534938</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.1064793166329098</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-0.04613413275717124</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.06097964293644918</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.01991828404009555</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-0.07216822196090436</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.2432388761723343</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-0.1050297328403207</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-0.09223632430093449</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>-0.01399390515758598</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>-0.02071822565696174</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-0.04481183372135537</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.02026315752943795</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.0699021580394064</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0.05807575369095936</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.1619083268834182</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>-0.03846608167488708</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>-0.07636058453363764</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>-0.06851210580353395</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.002226543794065762</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0.06562853534023264</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>-0.07212853004235267</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>0.1004584927622055</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>0.03650349465188414</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>-0.06248877815009718</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>-0.003929736350940091</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>0.06837923266734859</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>-0.03093544367386237</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>-0.01243639979336099</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>-0.01681630782781365</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>-0.02629908806474939</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>-0.01482057690703066</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>-0.02146890654326647</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>0.03102927730278724</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>-0.01044282629403498</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0.02663036916940175</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>-0.02033096619267932</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>-0.02586847692215741</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>0.03588493470202741</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>-0.0379261295103732</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>-0.02783907988881224</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>0.04457929896783316</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>-0.07014806052570631</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>-0.008723343313503471</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>0.05111681997350929</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>-0.062732692020456</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>0.02253889683855139</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>0.04711148695033097</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>-0.01556740577559344</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>-0.0007360968758035229</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>0.0483029259662929</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>-0.04257255475824707</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>0.04395152204113223</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.3551459068231119</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.06624780114624799</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.01098429745012845</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.1016867037361101</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.3409251365716396</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.1032063220192036</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.06126922043566328</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.03776431422260999</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.04734494179420583</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.08232009950528989</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.06073201395036021</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.03605285815306809</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0.02133804096339007</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-0.1560318573565459</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.1148470254943638</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-0.04483845874131912</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.1068143413943105</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-0.05825390522548553</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.05439081277967019</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-0.08972461437830465</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.3335868263825847</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-0.009629259157114704</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0.08780535925609508</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-0.09812328642952726</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-0.01140236750930894</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-0.06695445276446872</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-0.05139082285314105</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>-0.0193104478582178</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.02219673109581477</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0.002232439171185603</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0.08692222162543835</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0.01729389730064205</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.2021413850493318</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>-0.03783706356007563</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>-0.02168645206373425</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>-0.08911401918887189</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>-0.09791737837251817</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0.03225610680804188</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.01974887851725612</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0.0362721956170256</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>-0.1016975543828742</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0.08915633568965595</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0.1217066319068705</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0.08301250285341864</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>-0.09174127876333839</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0.02623950052228598</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0.01432238616037525</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0.03659182256535285</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>-0.02671024991865038</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>-0.04319015153530167</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>0.1105160589223386</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>-0.009201923717437098</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>-0.08322142236751776</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0.03760436146061279</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>-0.007618156034576174</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0.005632129299275784</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>0.06467366230099063</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>0.008505927472670033</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>-0.00783106266820404</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>0.02133215047088441</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>-0.05904384290557171</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>0.04834120355707774</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>0.02638423161580142</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>-0.001698439665190165</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>-0.02245930463353922</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>0.01060469725224102</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>0.006178462308005487</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0.08030112938705838</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>-0.1071331813787448</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>0.0227492879967365</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>0.0106235942148288</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>0.02900336782100998</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>-0.03317414728052074</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>0.03266659876532933</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>0.003943278395733587</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>0.02763113854297916</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>-0.09027110150367833</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>0.16897490766619</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>-0.009100134241440631</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>0.1117377186749091</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>-0.09272021558676033</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>-0.07432465772898592</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0.0006097985196584007</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.5180481033177419</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.06147994282379924</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.209093573008236</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.643979264321317</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.07181431967098559</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.1110065846545526</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.0825688503498333</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.06198560141531508</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.04076128392298476</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.01791058539452526</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0.1630568678752857</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-0.07516107783948249</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.07902847171312587</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.0130707113805475</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-0.1534995418770378</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0.4745401595134287</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-0.223957936144948</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-0.1342807609504265</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0.006898298446222749</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>-0.05945762377877578</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>-0.1059214426079688</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.0813423821057223</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0.09997891046611389</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>-0.001708946803609338</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0.2973278672917199</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>-0.08465652771461853</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>-0.08813786074675257</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>-0.1509462880393314</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0.03739010556203573</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0.06568594532480369</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>-0.2408495160815819</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>0.2585020257848481</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>0.1242683961836985</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>-0.1537191133321979</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>-0.005172126432719299</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>0.05930396982316762</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>0.002126596608247948</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>-0.0605692745775366</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>0.01037031573494669</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>-0.08112097273615204</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR17" t="n">
+        <v>-0.03961490702160498</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>-0.005410691007561073</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX17" t="n">
+        <v>0.05379098968229609</v>
+      </c>
+      <c r="DY17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA17" t="n">
+        <v>-0.05268054833391958</v>
+      </c>
+      <c r="EB17" t="n">
+        <v>-0.05592312843756012</v>
+      </c>
+      <c r="EC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG17" t="n">
+        <v>-0.03698881960208775</v>
+      </c>
+      <c r="EH17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ17" t="n">
+        <v>-0.05929001476202606</v>
+      </c>
+      <c r="EK17" t="n">
+        <v>0.02433424203969798</v>
+      </c>
+      <c r="EL17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP17" t="n">
+        <v>-0.0693866785405625</v>
+      </c>
+      <c r="EQ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER17" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES17" t="n">
+        <v>-0.03800474644069021</v>
+      </c>
+      <c r="ET17" t="n">
+        <v>-0.09810446638067608</v>
+      </c>
+      <c r="EU17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY17" t="n">
+        <v>-0.163350001726733</v>
+      </c>
+      <c r="EZ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB17" t="n">
+        <v>0.007860646053425525</v>
+      </c>
+      <c r="FC17" t="n">
+        <v>0.05230941185838079</v>
+      </c>
+      <c r="FD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH17" t="n">
+        <v>-0.1325234891259381</v>
+      </c>
+      <c r="FI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK17" t="n">
+        <v>0.07938080095738352</v>
+      </c>
+      <c r="FL17" t="n">
+        <v>0.1221670086556265</v>
+      </c>
+      <c r="FM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ17" t="n">
+        <v>-0.1169374370399837</v>
+      </c>
+      <c r="FR17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT17" t="n">
+        <v>0.01811202582686371</v>
+      </c>
+      <c r="FU17" t="n">
+        <v>0.07554990158658766</v>
+      </c>
+      <c r="FV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ17" t="n">
+        <v>-0.07945850591444292</v>
+      </c>
+      <c r="GA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD17" t="n">
+        <v>-0.04679376899199307</v>
+      </c>
+      <c r="GE17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG17" t="n">
         <v>0</v>
       </c>
     </row>
